--- a/Services/PCB Service/04_Tracking/PCB_Job_Tracker.xlsx
+++ b/Services/PCB Service/04_Tracking/PCB_Job_Tracker.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" min="1" max="1"/>
@@ -841,47 +841,6 @@
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TEST-001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HTTP Test</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SMPS 24V</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>500</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
